--- a/W01_Kahoot匯入.xlsx
+++ b/W01_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>細胞</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>脂質</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>蛋白質</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>分子</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>單體</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>核酸</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>分子</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>細胞</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -566,17 +566,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>核酸</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>脂質</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>蛋白質</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>核酸</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -601,25 +601,25 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>碳水化合物</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>核酸</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>蛋白質</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>碳水化合物</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>核酸</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>單體</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>核酸</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>脂質</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>醣類</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>大分子</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>蛋白質</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>脂質</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>大分子</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -701,30 +701,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>粒線體</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>細胞核</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>粒線體</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>細胞質</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>細胞膜</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>胞器</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>細胞核</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>粒線體</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>胞器</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>細胞膜</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,22 +806,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>粒線體</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>細胞膜</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>細胞核</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>細胞質</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>粒線體</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,17 +841,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>大分子</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>聚合物</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>大分子</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>分子</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>官能基</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>大分子</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>聚合物</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>單體</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>官能基</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>胞器</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>官能基</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>側鏈</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>單體</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>胞器</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>大分子</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>聚合物</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>官能基</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>大分子</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>單體</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -981,19 +981,19 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>核苷酸</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>單醣</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>脂肪酸</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>核苷酸</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>胺基酸</t>
@@ -1005,6 +1005,146 @@
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:細胞構造) 圖正中央、含核仁的紫色構造是什麼?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>內質網</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>粒線體</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>高基氏體</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:細胞構造) 圖左下方、像一疊薄餅的構造是什麼?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>內質網</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>高基氏體</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>粒線體</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>細胞核—ATP合成</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>粒線體—ATP合成</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>蛋白質—由核苷酸組成</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>核酸—細胞能量來源</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>沒有細胞核的細胞稱為什麼?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>原核細胞</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>真核細胞</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>大分子</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
